--- a/ExportExcel/Add User Test.xlsx
+++ b/ExportExcel/Add User Test.xlsx
@@ -41,19 +41,19 @@
     <t>PASSED</t>
   </si>
   <si>
-    <t>4000 ms</t>
+    <t>2318 ms</t>
   </si>
   <si>
     <t>testInvalidEmailCreation</t>
   </si>
   <si>
-    <t>4489 ms</t>
+    <t>3059 ms</t>
   </si>
   <si>
     <t>testValidUserCreation</t>
   </si>
   <si>
-    <t>4035 ms</t>
+    <t>3372 ms</t>
   </si>
 </sst>
 </file>
